--- a/outputs/per-fund/vc-investments-founders-fund.xlsx
+++ b/outputs/per-fund/vc-investments-founders-fund.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Founders Fund. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Founders Fund. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -9848,11 +9848,11 @@
         <v>1</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>founders-fund</t>
+          <t>blockchain-capital, digital-currency-group, founders-fund</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -9907,11 +9907,11 @@
         <v>0</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, pantera</t>
+          <t>digital-currency-group, founders-fund, pantera</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -10033,11 +10033,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>founders-fund</t>
+          <t>digital-currency-group, founders-fund</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -10096,11 +10096,11 @@
         <v>1</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, founders-fund</t>
+          <t>blockchain-capital, coinbase-ventures, founders-fund</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -10159,11 +10159,11 @@
         <v>2</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, founders-fund, multicoin-capital, pantera, paradigm, semantic-ventures</t>
+          <t>coinbase-ventures, founders-fund, multicoin-capital, pantera, paradigm, semantic-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -10592,11 +10592,11 @@
         <v>1</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, pantera, paradigm</t>
+          <t>alameda-research, founders-fund, pantera, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -10785,11 +10785,11 @@
         <v>1</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>founders-fund</t>
+          <t>founders-fund, sequoia-capital</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -10848,11 +10848,11 @@
         <v>4</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, founders-fund, pantera</t>
+          <t>dragonfly, fenbushi-capital, founders-fund, pantera, spartan-group</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -11159,11 +11159,11 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>founders-fund</t>
+          <t>founders-fund, galaxy-digital</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -11224,11 +11224,11 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, paradigm</t>
+          <t>alameda-research, founders-fund, iosg-ventures, paradigm, sequoia-capital</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -11350,11 +11350,11 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, founders-fund</t>
+          <t>coinbase-ventures, founders-fund, mh-ventures</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -11850,11 +11850,11 @@
         <v>1</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, founders-fund, pantera</t>
+          <t>coinbase-ventures, founders-fund, pantera, yzi-labs</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -12037,11 +12037,11 @@
         <v>1</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, pantera</t>
+          <t>founders-fund, galaxy-digital, pantera</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -12226,11 +12226,11 @@
         <v>2</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, figment-capital, founders-fund</t>
+          <t>dragonfly, figment-capital, founders-fund, sevenx-ventures</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -12289,11 +12289,11 @@
         <v>1</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, maven11</t>
+          <t>1kx, cmt-digital, fenbushi-capital, founders-fund, maven11</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -12352,11 +12352,11 @@
         <v>1</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, founders-fund</t>
+          <t>dragonfly, founders-fund, parafi-capital</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -12415,11 +12415,11 @@
         <v>3</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, dragonfly, figment-capital, founders-fund</t>
+          <t>alliance-dao, cyber-fund, dragonfly, figment-capital, foresight-ventures, founders-fund, hashkey-capital, longhash-ventures, mirana-ventures, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -12474,11 +12474,11 @@
         <v>1</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>founders-fund</t>
+          <t>1kx, fenbushi-capital, founders-fund</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -12537,11 +12537,11 @@
         <v>3</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, founders-fund, framework-ventures, pantera, robot-ventures</t>
+          <t>arrington-capital, delphi-ventures, foresight-ventures, founders-fund, framework-ventures, hack-vc, hashkey-capital, hypersphere, mh-ventures, mirana-ventures, pantera, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -12600,11 +12600,11 @@
         <v>1</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, founders-fund</t>
+          <t>dragonfly, founders-fund, sequoia-capital</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -12722,11 +12722,11 @@
         <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, founders-fund, framework-ventures</t>
+          <t>cyber-fund, founders-fund, framework-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -12783,11 +12783,11 @@
         <v>1</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, founders-fund</t>
+          <t>blockchain-capital, coinbase-ventures, dragonfly, founders-fund, parafi-capital</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -12846,11 +12846,11 @@
         <v>1</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, maven11</t>
+          <t>founders-fund, maven11, mirana-ventures</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -12972,11 +12972,11 @@
         <v>2</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, pantera</t>
+          <t>amber-group, digital-currency-group, founders-fund, pantera</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -13151,11 +13151,11 @@
         <v>1</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, founders-fund</t>
+          <t>coinbase-ventures, founders-fund, galaxy-digital, mirana-ventures</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -13338,11 +13338,11 @@
         <v>1</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, founders-fund</t>
+          <t>blockchain-capital, coinbase-ventures, dragonfly, founders-fund</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -13511,11 +13511,11 @@
         <v>0</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>founders-fund</t>
+          <t>founders-fund, sequoia-capital</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -16347,19 +16347,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
